--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/130.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/130.xlsx
@@ -426,13 +426,13 @@
         <v>-14.67207881351245</v>
       </c>
       <c r="E2">
-        <v>-7.437427404211159</v>
+        <v>-6.183791830771743</v>
       </c>
       <c r="F2">
-        <v>-5.191911300832009</v>
+        <v>-5.600757831055525</v>
       </c>
       <c r="G2">
-        <v>-6.033774966179685</v>
+        <v>-4.1624261997414</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-14.57017034082709</v>
       </c>
       <c r="E3">
-        <v>-7.76029854401004</v>
+        <v>-6.682576071872587</v>
       </c>
       <c r="F3">
-        <v>-5.072468176654946</v>
+        <v>-5.643258049023556</v>
       </c>
       <c r="G3">
-        <v>-6.275775845100409</v>
+        <v>-4.212610759571213</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-14.45359073316772</v>
       </c>
       <c r="E4">
-        <v>-8.631993562694523</v>
+        <v>-7.624960569816804</v>
       </c>
       <c r="F4">
-        <v>-5.274943535819021</v>
+        <v>-5.817194494426383</v>
       </c>
       <c r="G4">
-        <v>-5.220844024647331</v>
+        <v>-4.642117627290717</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-14.3398494782223</v>
       </c>
       <c r="E5">
-        <v>-9.481544343481497</v>
+        <v>-7.79851433616077</v>
       </c>
       <c r="F5">
-        <v>-5.291726259399739</v>
+        <v>-5.723971683650132</v>
       </c>
       <c r="G5">
-        <v>-5.741410757970029</v>
+        <v>-4.241041724662473</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-14.22770031048645</v>
       </c>
       <c r="E6">
-        <v>-9.297806039094279</v>
+        <v>-9.98969799730421</v>
       </c>
       <c r="F6">
-        <v>-5.7425445091883</v>
+        <v>-5.472408928930964</v>
       </c>
       <c r="G6">
-        <v>-5.416589961293358</v>
+        <v>-4.056588058850901</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-14.10889680473439</v>
       </c>
       <c r="E7">
-        <v>-10.58014760926832</v>
+        <v>-9.978775317997711</v>
       </c>
       <c r="F7">
-        <v>-5.538092665401146</v>
+        <v>-5.551056615254957</v>
       </c>
       <c r="G7">
-        <v>-5.728072569992305</v>
+        <v>-4.266804390049082</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.95696568676837</v>
       </c>
       <c r="E8">
-        <v>-9.638863530507965</v>
+        <v>-10.31452996634841</v>
       </c>
       <c r="F8">
-        <v>-5.143414531235113</v>
+        <v>-5.515691125727238</v>
       </c>
       <c r="G8">
-        <v>-5.481042972397429</v>
+        <v>-3.94248679629438</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.74046532421379</v>
       </c>
       <c r="E9">
-        <v>-10.98614794642601</v>
+        <v>-11.52514503671496</v>
       </c>
       <c r="F9">
-        <v>-5.076459250801634</v>
+        <v>-5.309847624703381</v>
       </c>
       <c r="G9">
-        <v>-5.19564084145686</v>
+        <v>-3.293527175322128</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.42891001545626</v>
       </c>
       <c r="E10">
-        <v>-12.76338832700231</v>
+        <v>-12.82883383336116</v>
       </c>
       <c r="F10">
-        <v>-5.09134749813215</v>
+        <v>-5.639611575716433</v>
       </c>
       <c r="G10">
-        <v>-4.826544808737975</v>
+        <v>-3.076858590867907</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.00345729752677</v>
       </c>
       <c r="E11">
-        <v>-13.52452065278952</v>
+        <v>-12.68367812751929</v>
       </c>
       <c r="F11">
-        <v>-5.176001676493843</v>
+        <v>-5.126004733530475</v>
       </c>
       <c r="G11">
-        <v>-4.384070534141146</v>
+        <v>-3.128635523102108</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.46614096588684</v>
       </c>
       <c r="E12">
-        <v>-13.82245801470216</v>
+        <v>-13.35437682737333</v>
       </c>
       <c r="F12">
-        <v>-5.11053083044618</v>
+        <v>-5.295093572892119</v>
       </c>
       <c r="G12">
-        <v>-4.059322569466339</v>
+        <v>-3.354785509980802</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-11.83949451194059</v>
       </c>
       <c r="E13">
-        <v>-13.70098169944641</v>
+        <v>-14.4867217529913</v>
       </c>
       <c r="F13">
-        <v>-5.037699111657242</v>
+        <v>-5.497645970224654</v>
       </c>
       <c r="G13">
-        <v>-4.0427797734066</v>
+        <v>-2.798017961186174</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.17356786967998</v>
       </c>
       <c r="E14">
-        <v>-16.04096648800789</v>
+        <v>-14.98482219451698</v>
       </c>
       <c r="F14">
-        <v>-5.0784315935877</v>
+        <v>-4.98872437406893</v>
       </c>
       <c r="G14">
-        <v>-4.319657249583546</v>
+        <v>-2.521037858097511</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.52411848916519</v>
       </c>
       <c r="E15">
-        <v>-17.24167325724565</v>
+        <v>-16.1269350385695</v>
       </c>
       <c r="F15">
-        <v>-4.589124080795463</v>
+        <v>-4.897551772614608</v>
       </c>
       <c r="G15">
-        <v>-3.386176102784171</v>
+        <v>-2.007602039866403</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.945573949691486</v>
       </c>
       <c r="E16">
-        <v>-16.18311981558267</v>
+        <v>-17.40320392509925</v>
       </c>
       <c r="F16">
-        <v>-4.239470200073791</v>
+        <v>-4.605102459628062</v>
       </c>
       <c r="G16">
-        <v>-3.359138877364944</v>
+        <v>-1.718283533552876</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.477176452924484</v>
       </c>
       <c r="E17">
-        <v>-17.96208101628188</v>
+        <v>-17.71801438116448</v>
       </c>
       <c r="F17">
-        <v>-4.425755946717552</v>
+        <v>-4.591774028117018</v>
       </c>
       <c r="G17">
-        <v>-2.333786781305254</v>
+        <v>-1.847547094679259</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.146113553296054</v>
       </c>
       <c r="E18">
-        <v>-17.88917258475839</v>
+        <v>-18.66517641918679</v>
       </c>
       <c r="F18">
-        <v>-4.187507541263581</v>
+        <v>-4.085071628233394</v>
       </c>
       <c r="G18">
-        <v>-3.265255116416752</v>
+        <v>-1.544767910203055</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-8.959471345037878</v>
       </c>
       <c r="E19">
-        <v>-19.16592601800696</v>
+        <v>-18.47385744931073</v>
       </c>
       <c r="F19">
-        <v>-3.908786761243631</v>
+        <v>-3.750867627941336</v>
       </c>
       <c r="G19">
-        <v>-3.472763421363809</v>
+        <v>-2.371589900818191</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.916835331922288</v>
       </c>
       <c r="E20">
-        <v>-19.21892727779274</v>
+        <v>-20.40386590053579</v>
       </c>
       <c r="F20">
-        <v>-3.66222071869815</v>
+        <v>-3.442939441666079</v>
       </c>
       <c r="G20">
-        <v>-2.487651006333961</v>
+        <v>-2.950574520726868</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.007445165202984</v>
       </c>
       <c r="E21">
-        <v>-19.68514726230442</v>
+        <v>-20.87283014029613</v>
       </c>
       <c r="F21">
-        <v>-3.160370895060125</v>
+        <v>-3.184186457890611</v>
       </c>
       <c r="G21">
-        <v>-3.122554050946468</v>
+        <v>-2.529046067757007</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.214593665578457</v>
       </c>
       <c r="E22">
-        <v>-20.75666119657736</v>
+        <v>-20.31377191015319</v>
       </c>
       <c r="F22">
-        <v>-2.796029231919416</v>
+        <v>-2.853697685400109</v>
       </c>
       <c r="G22">
-        <v>-2.770149788836589</v>
+        <v>-3.13662386948837</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-9.511486866599494</v>
       </c>
       <c r="E23">
-        <v>-21.38183967570629</v>
+        <v>-20.86634536551714</v>
       </c>
       <c r="F23">
-        <v>-2.605080605165297</v>
+        <v>-2.626397811908939</v>
       </c>
       <c r="G23">
-        <v>-3.235953477848663</v>
+        <v>-3.245044235899501</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-9.868594367197728</v>
       </c>
       <c r="E24">
-        <v>-21.18922556226404</v>
+        <v>-21.23865838453177</v>
       </c>
       <c r="F24">
-        <v>-2.312724069327864</v>
+        <v>-2.575604807871482</v>
       </c>
       <c r="G24">
-        <v>-4.019930388094551</v>
+        <v>-2.873766553670237</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.25142644703873</v>
       </c>
       <c r="E25">
-        <v>-21.02131880300764</v>
+        <v>-21.32569112648519</v>
       </c>
       <c r="F25">
-        <v>-2.476149360756568</v>
+        <v>-2.301145978138936</v>
       </c>
       <c r="G25">
-        <v>-4.534101147435377</v>
+        <v>-3.778561823371828</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.62127218125642</v>
       </c>
       <c r="E26">
-        <v>-21.36156116909994</v>
+        <v>-21.85861100465585</v>
       </c>
       <c r="F26">
-        <v>-2.057242308426052</v>
+        <v>-2.107517582836759</v>
       </c>
       <c r="G26">
-        <v>-4.884429697492132</v>
+        <v>-3.913784366468899</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.94272355372683</v>
       </c>
       <c r="E27">
-        <v>-21.9882883863395</v>
+        <v>-21.44922336894043</v>
       </c>
       <c r="F27">
-        <v>-2.384590740092541</v>
+        <v>-1.98745732494461</v>
       </c>
       <c r="G27">
-        <v>-4.661050637229809</v>
+        <v>-4.643792763333589</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-11.18914256657206</v>
       </c>
       <c r="E28">
-        <v>-21.46627760205331</v>
+        <v>-21.52528814684727</v>
       </c>
       <c r="F28">
-        <v>-2.012899801354195</v>
+        <v>-1.802011542847288</v>
       </c>
       <c r="G28">
-        <v>-4.578508805299161</v>
+        <v>-4.752067465740992</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-11.34995428273405</v>
       </c>
       <c r="E29">
-        <v>-21.48538323389167</v>
+        <v>-21.27731796713525</v>
       </c>
       <c r="F29">
-        <v>-2.11745384983334</v>
+        <v>-2.287823345199711</v>
       </c>
       <c r="G29">
-        <v>-4.703114428851789</v>
+        <v>-4.739229170139698</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-11.42438375391002</v>
       </c>
       <c r="E30">
-        <v>-20.97679031809022</v>
+        <v>-20.61374255689528</v>
       </c>
       <c r="F30">
-        <v>-1.918191727824724</v>
+        <v>-1.880065289743474</v>
       </c>
       <c r="G30">
-        <v>-4.622684724975195</v>
+        <v>-5.147929259144883</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-11.42731496386427</v>
       </c>
       <c r="E31">
-        <v>-20.88862092916088</v>
+        <v>-20.80857562260129</v>
       </c>
       <c r="F31">
-        <v>-2.13463087629779</v>
+        <v>-1.906994685641083</v>
       </c>
       <c r="G31">
-        <v>-5.26313955445706</v>
+        <v>-4.80399337252446</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-11.38136260530537</v>
       </c>
       <c r="E32">
-        <v>-20.13492435769426</v>
+        <v>-20.32652409295879</v>
       </c>
       <c r="F32">
-        <v>-1.676363118455853</v>
+        <v>-1.71504787616659</v>
       </c>
       <c r="G32">
-        <v>-4.693570126062069</v>
+        <v>-4.651605650806268</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-11.31566297613556</v>
       </c>
       <c r="E33">
-        <v>-20.56455880069798</v>
+        <v>-19.76015237729347</v>
       </c>
       <c r="F33">
-        <v>-2.296467359047924</v>
+        <v>-1.770893092993722</v>
       </c>
       <c r="G33">
-        <v>-4.223234300206734</v>
+        <v>-3.804062955660834</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-11.25396087967206</v>
       </c>
       <c r="E34">
-        <v>-20.17426321139889</v>
+        <v>-19.84858441771526</v>
       </c>
       <c r="F34">
-        <v>-2.0890358777129</v>
+        <v>-1.708488863071224</v>
       </c>
       <c r="G34">
-        <v>-4.756808166953229</v>
+        <v>-3.796998251480029</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-11.21872810102217</v>
       </c>
       <c r="E35">
-        <v>-20.1259760930551</v>
+        <v>-18.96022461468255</v>
       </c>
       <c r="F35">
-        <v>-1.912944020327989</v>
+        <v>-1.6628839240775</v>
       </c>
       <c r="G35">
-        <v>-4.464973646029855</v>
+        <v>-3.946095290932186</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-11.22168288123543</v>
       </c>
       <c r="E36">
-        <v>-18.58899842942976</v>
+        <v>-18.992372251663</v>
       </c>
       <c r="F36">
-        <v>-1.81241583742645</v>
+        <v>-1.778249823897984</v>
       </c>
       <c r="G36">
-        <v>-3.519793031294696</v>
+        <v>-3.585374938427658</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-11.26544311118737</v>
       </c>
       <c r="E37">
-        <v>-19.45041834059084</v>
+        <v>-18.71017586540101</v>
       </c>
       <c r="F37">
-        <v>-2.041321086944246</v>
+        <v>-1.995562071613601</v>
       </c>
       <c r="G37">
-        <v>-3.957801379959049</v>
+        <v>-2.840475707727327</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-11.33958728143252</v>
       </c>
       <c r="E38">
-        <v>-17.72406442243873</v>
+        <v>-17.69890422085211</v>
       </c>
       <c r="F38">
-        <v>-1.979221696225978</v>
+        <v>-1.584451613278234</v>
       </c>
       <c r="G38">
-        <v>-3.177648149811018</v>
+        <v>-3.007181538902866</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-11.4275196008757</v>
       </c>
       <c r="E39">
-        <v>-18.19000364156194</v>
+        <v>-17.89318028425518</v>
       </c>
       <c r="F39">
-        <v>-1.935217991421865</v>
+        <v>-1.954146186575834</v>
       </c>
       <c r="G39">
-        <v>-3.809131400881458</v>
+        <v>-2.665460407248216</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-11.50972011994742</v>
       </c>
       <c r="E40">
-        <v>-17.42266277791021</v>
+        <v>-17.913735027776</v>
       </c>
       <c r="F40">
-        <v>-2.021055906802158</v>
+        <v>-2.072266408010627</v>
       </c>
       <c r="G40">
-        <v>-2.747151428975272</v>
+        <v>-2.159953345583663</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-11.56607649910884</v>
       </c>
       <c r="E41">
-        <v>-17.09478767433286</v>
+        <v>-17.33845580373758</v>
       </c>
       <c r="F41">
-        <v>-1.901365100771658</v>
+        <v>-1.844636015925739</v>
       </c>
       <c r="G41">
-        <v>-2.754768994261135</v>
+        <v>-2.030467977906149</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-11.58100539853355</v>
       </c>
       <c r="E42">
-        <v>-16.92595257790488</v>
+        <v>-15.97954226656785</v>
       </c>
       <c r="F42">
-        <v>-2.055945085073268</v>
+        <v>-2.232616799640138</v>
       </c>
       <c r="G42">
-        <v>-3.051890456410724</v>
+        <v>-1.506239781217017</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-11.5428214457978</v>
       </c>
       <c r="E43">
-        <v>-16.48495619361592</v>
+        <v>-16.35244398720347</v>
       </c>
       <c r="F43">
-        <v>-2.268594452678526</v>
+        <v>-2.212169378669435</v>
       </c>
       <c r="G43">
-        <v>-2.361138508550712</v>
+        <v>-1.413117445742858</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-11.45098188284346</v>
       </c>
       <c r="E44">
-        <v>-16.1474807251423</v>
+        <v>-16.16392814273816</v>
       </c>
       <c r="F44">
-        <v>-2.119844518157819</v>
+        <v>-2.31426151922746</v>
       </c>
       <c r="G44">
-        <v>-2.961075571177437</v>
+        <v>-1.495387812939286</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-11.30713280137181</v>
       </c>
       <c r="E45">
-        <v>-15.65149960945221</v>
+        <v>-14.72449833771205</v>
       </c>
       <c r="F45">
-        <v>-2.574304271049086</v>
+        <v>-2.41942938795208</v>
       </c>
       <c r="G45">
-        <v>-2.661742664607615</v>
+        <v>-1.008568780843919</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-11.12051760275897</v>
       </c>
       <c r="E46">
-        <v>-16.01447038658901</v>
+        <v>-14.73117330839935</v>
       </c>
       <c r="F46">
-        <v>-2.553445979846595</v>
+        <v>-2.466189899472709</v>
       </c>
       <c r="G46">
-        <v>-1.925212493030561</v>
+        <v>-0.2297828060036077</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-10.90232060919578</v>
       </c>
       <c r="E47">
-        <v>-15.33418037878673</v>
+        <v>-14.22263473428599</v>
       </c>
       <c r="F47">
-        <v>-2.313287359161768</v>
+        <v>-2.707733550455017</v>
       </c>
       <c r="G47">
-        <v>-2.362800402411426</v>
+        <v>-0.6936465153296687</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-10.66817246426793</v>
       </c>
       <c r="E48">
-        <v>-14.04222938676841</v>
+        <v>-13.89180706565563</v>
       </c>
       <c r="F48">
-        <v>-2.638699896207914</v>
+        <v>-2.565275894725975</v>
       </c>
       <c r="G48">
-        <v>-2.047321965246578</v>
+        <v>-0.906296097499214</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-10.42867577688072</v>
       </c>
       <c r="E49">
-        <v>-13.13188384242846</v>
+        <v>-13.63053675778309</v>
       </c>
       <c r="F49">
-        <v>-2.580009237352167</v>
+        <v>-2.628044606305704</v>
       </c>
       <c r="G49">
-        <v>-2.17086821422664</v>
+        <v>-0.883992952201144</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-10.1951890222649</v>
       </c>
       <c r="E50">
-        <v>-12.13824607566544</v>
+        <v>-13.08176722058558</v>
       </c>
       <c r="F50">
-        <v>-2.664602116526052</v>
+        <v>-2.708281101308267</v>
       </c>
       <c r="G50">
-        <v>-2.041624516373493</v>
+        <v>-0.2700324186700668</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-9.975087172787559</v>
       </c>
       <c r="E51">
-        <v>-12.56491889666814</v>
+        <v>-13.0695584546609</v>
       </c>
       <c r="F51">
-        <v>-2.539480533802798</v>
+        <v>-2.700042159120024</v>
       </c>
       <c r="G51">
-        <v>-2.492206316995998</v>
+        <v>-0.4213409025424564</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-9.773794801720125</v>
       </c>
       <c r="E52">
-        <v>-12.54812278657369</v>
+        <v>-11.69393484840286</v>
       </c>
       <c r="F52">
-        <v>-2.772906184237671</v>
+        <v>-2.925164254709234</v>
       </c>
       <c r="G52">
-        <v>-1.811167509748208</v>
+        <v>-0.5590893918859913</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-9.591799178758913</v>
       </c>
       <c r="E53">
-        <v>-11.50502049822487</v>
+        <v>-11.45982179915432</v>
       </c>
       <c r="F53">
-        <v>-2.88889501634506</v>
+        <v>-3.040101888582471</v>
       </c>
       <c r="G53">
-        <v>-1.491246320469658</v>
+        <v>-0.686631469331953</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-9.42684871647509</v>
       </c>
       <c r="E54">
-        <v>-11.42194111408015</v>
+        <v>-11.05816879704399</v>
       </c>
       <c r="F54">
-        <v>-3.047104078238335</v>
+        <v>-3.236183079764337</v>
       </c>
       <c r="G54">
-        <v>-2.144784425922722</v>
+        <v>-0.8256776925268822</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-9.2767779132394</v>
       </c>
       <c r="E55">
-        <v>-10.58549120859737</v>
+        <v>-9.96987233809863</v>
       </c>
       <c r="F55">
-        <v>-2.566356085819225</v>
+        <v>-2.800122195256649</v>
       </c>
       <c r="G55">
-        <v>-2.954090320089574</v>
+        <v>-0.6306435231717987</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-9.136218723528254</v>
       </c>
       <c r="E56">
-        <v>-10.10333099557868</v>
+        <v>-10.62904154312914</v>
       </c>
       <c r="F56">
-        <v>-2.859440756603719</v>
+        <v>-2.883766593754329</v>
       </c>
       <c r="G56">
-        <v>-3.010972113545332</v>
+        <v>-0.7726857900797682</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-9.00000361925996</v>
       </c>
       <c r="E57">
-        <v>-10.34006150280366</v>
+        <v>-9.820668176493907</v>
       </c>
       <c r="F57">
-        <v>-2.949816468616547</v>
+        <v>-3.073836322694078</v>
       </c>
       <c r="G57">
-        <v>-3.657627594822252</v>
+        <v>-0.5051440523235673</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.860967069652039</v>
       </c>
       <c r="E58">
-        <v>-10.049202145765</v>
+        <v>-9.848495649271042</v>
       </c>
       <c r="F58">
-        <v>-2.40636851911214</v>
+        <v>-2.887335200525589</v>
       </c>
       <c r="G58">
-        <v>-3.32771848965172</v>
+        <v>-1.012528193308887</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.718209087679428</v>
       </c>
       <c r="E59">
-        <v>-9.359031007677983</v>
+        <v>-10.27518205569577</v>
       </c>
       <c r="F59">
-        <v>-2.803827482649371</v>
+        <v>-3.081357070344095</v>
       </c>
       <c r="G59">
-        <v>-3.365253454975977</v>
+        <v>-1.181071377258723</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-8.569721429940634</v>
       </c>
       <c r="E60">
-        <v>-8.09967597156688</v>
+        <v>-9.443305908960729</v>
       </c>
       <c r="F60">
-        <v>-2.860780226694045</v>
+        <v>-2.692748384138374</v>
       </c>
       <c r="G60">
-        <v>-3.579753632101975</v>
+        <v>-1.278159746288929</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-8.417597246588405</v>
       </c>
       <c r="E61">
-        <v>-8.455455531979501</v>
+        <v>-8.632174701654829</v>
       </c>
       <c r="F61">
-        <v>-3.251197238940077</v>
+        <v>-2.869453233401356</v>
       </c>
       <c r="G61">
-        <v>-2.827273252116713</v>
+        <v>-1.408740904539941</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-8.263459823495035</v>
       </c>
       <c r="E62">
-        <v>-7.977620011638141</v>
+        <v>-8.62154184468482</v>
       </c>
       <c r="F62">
-        <v>-2.725439075322454</v>
+        <v>-2.687808000948078</v>
       </c>
       <c r="G62">
-        <v>-3.245451433000832</v>
+        <v>-1.381971833309395</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-8.111462724297231</v>
       </c>
       <c r="E63">
-        <v>-9.126598022286286</v>
+        <v>-7.754420584748084</v>
       </c>
       <c r="F63">
-        <v>-2.941897276245784</v>
+        <v>-3.029080460288224</v>
       </c>
       <c r="G63">
-        <v>-3.861457883675179</v>
+        <v>-1.872276869857614</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.962110455116076</v>
       </c>
       <c r="E64">
-        <v>-8.277269136725689</v>
+        <v>-7.683386941463767</v>
       </c>
       <c r="F64">
-        <v>-3.144598779710823</v>
+        <v>-2.948039620537542</v>
       </c>
       <c r="G64">
-        <v>-3.433857890186294</v>
+        <v>-1.949190774371502</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.81805295647793</v>
       </c>
       <c r="E65">
-        <v>-8.024874637908182</v>
+        <v>-8.522875453005698</v>
       </c>
       <c r="F65">
-        <v>-3.141594291140869</v>
+        <v>-2.899759883200179</v>
       </c>
       <c r="G65">
-        <v>-3.741609514062483</v>
+        <v>-2.373125993948413</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.681573932508482</v>
       </c>
       <c r="E66">
-        <v>-6.950290398258043</v>
+        <v>-7.499286359155937</v>
       </c>
       <c r="F66">
-        <v>-3.271725839916255</v>
+        <v>-2.75174636730056</v>
       </c>
       <c r="G66">
-        <v>-3.744201671219732</v>
+        <v>-2.434748488616407</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.553546836210939</v>
       </c>
       <c r="E67">
-        <v>-6.915606815833296</v>
+        <v>-7.436562465675694</v>
       </c>
       <c r="F67">
-        <v>-2.761143367117918</v>
+        <v>-2.994289029370644</v>
       </c>
       <c r="G67">
-        <v>-3.665145843741936</v>
+        <v>-2.319786484219676</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.431184493503241</v>
       </c>
       <c r="E68">
-        <v>-6.92706838354671</v>
+        <v>-7.709842286616578</v>
       </c>
       <c r="F68">
-        <v>-3.002968663017178</v>
+        <v>-2.889971065601297</v>
       </c>
       <c r="G68">
-        <v>-3.424618157586188</v>
+        <v>-1.772149420022358</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.309617436362834</v>
       </c>
       <c r="E69">
-        <v>-6.388053179361723</v>
+        <v>-6.781758709588583</v>
       </c>
       <c r="F69">
-        <v>-2.859594832940639</v>
+        <v>-2.935029282109173</v>
       </c>
       <c r="G69">
-        <v>-4.147141410986586</v>
+        <v>-2.265291594097733</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.186010910362032</v>
       </c>
       <c r="E70">
-        <v>-6.962376895384516</v>
+        <v>-7.589430162752622</v>
       </c>
       <c r="F70">
-        <v>-2.678140124990005</v>
+        <v>-3.133483745900059</v>
       </c>
       <c r="G70">
-        <v>-4.496913789392743</v>
+        <v>-2.720604164295856</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.055606472269679</v>
       </c>
       <c r="E71">
-        <v>-7.944589322226193</v>
+        <v>-7.487163634237403</v>
       </c>
       <c r="F71">
-        <v>-3.662319294419083</v>
+        <v>-3.03003805300586</v>
       </c>
       <c r="G71">
-        <v>-3.753557272913713</v>
+        <v>-2.143897199718197</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.91446010804513</v>
       </c>
       <c r="E72">
-        <v>-7.768920758520645</v>
+        <v>-6.722802506482723</v>
       </c>
       <c r="F72">
-        <v>-3.039215535461476</v>
+        <v>-3.320817377308362</v>
       </c>
       <c r="G72">
-        <v>-4.152365451847555</v>
+        <v>-2.197657148730422</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.757515239613645</v>
       </c>
       <c r="E73">
-        <v>-8.216705325347105</v>
+        <v>-7.325705421967924</v>
       </c>
       <c r="F73">
-        <v>-3.633101119387539</v>
+        <v>-3.239774880822875</v>
       </c>
       <c r="G73">
-        <v>-3.690415237843193</v>
+        <v>-2.715760836171902</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-6.583799341063829</v>
       </c>
       <c r="E74">
-        <v>-8.427532961248206</v>
+        <v>-7.985603711313663</v>
       </c>
       <c r="F74">
-        <v>-3.438892038536001</v>
+        <v>-3.638218773202035</v>
       </c>
       <c r="G74">
-        <v>-4.302713877513557</v>
+        <v>-1.868966324318343</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-6.390039893045512</v>
       </c>
       <c r="E75">
-        <v>-7.847222602587273</v>
+        <v>-7.326357522225028</v>
       </c>
       <c r="F75">
-        <v>-3.699439266105932</v>
+        <v>-3.678281105903627</v>
       </c>
       <c r="G75">
-        <v>-2.961750922467448</v>
+        <v>-1.959635545547903</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-6.173502126842128</v>
       </c>
       <c r="E76">
-        <v>-8.12729966301367</v>
+        <v>-8.618390026775481</v>
       </c>
       <c r="F76">
-        <v>-3.733534040037757</v>
+        <v>-3.514179866674239</v>
       </c>
       <c r="G76">
-        <v>-3.39558467320678</v>
+        <v>-2.186301977530722</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-5.931752675892726</v>
       </c>
       <c r="E77">
-        <v>-7.723817157404248</v>
+        <v>-8.220645097733778</v>
       </c>
       <c r="F77">
-        <v>-3.613747143388531</v>
+        <v>-3.704320835210629</v>
       </c>
       <c r="G77">
-        <v>-3.329016223503115</v>
+        <v>-2.480874319615072</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-5.667089877357077</v>
       </c>
       <c r="E78">
-        <v>-9.42133828154952</v>
+        <v>-8.099001228939738</v>
       </c>
       <c r="F78">
-        <v>-4.235255466728347</v>
+        <v>-3.923796778582358</v>
       </c>
       <c r="G78">
-        <v>-2.564313309386864</v>
+        <v>-1.850013451106016</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-5.383246722932073</v>
       </c>
       <c r="E79">
-        <v>-10.44001850957497</v>
+        <v>-9.736470259269293</v>
       </c>
       <c r="F79">
-        <v>-4.31124575042416</v>
+        <v>-3.944215206693964</v>
       </c>
       <c r="G79">
-        <v>-3.022181620741304</v>
+        <v>-1.588073156402262</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-5.087987100813504</v>
       </c>
       <c r="E80">
-        <v>-9.669688853078178</v>
+        <v>-9.875852160751379</v>
       </c>
       <c r="F80">
-        <v>-4.505266791875263</v>
+        <v>-4.087214614704436</v>
       </c>
       <c r="G80">
-        <v>-2.795713821490841</v>
+        <v>-1.442875939595367</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.791229410117613</v>
       </c>
       <c r="E81">
-        <v>-11.45270756648827</v>
+        <v>-10.08442461659666</v>
       </c>
       <c r="F81">
-        <v>-4.389084950163021</v>
+        <v>-4.182037002935493</v>
       </c>
       <c r="G81">
-        <v>-2.220284727491341</v>
+        <v>-1.418844689525797</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.502140445307428</v>
       </c>
       <c r="E82">
-        <v>-12.02374361038149</v>
+        <v>-11.50448613829197</v>
       </c>
       <c r="F82">
-        <v>-4.556956089442549</v>
+        <v>-4.3853208486847</v>
       </c>
       <c r="G82">
-        <v>-2.991618664322753</v>
+        <v>-2.01996692745558</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.227211835577868</v>
       </c>
       <c r="E83">
-        <v>-13.42888833869553</v>
+        <v>-12.6273620247599</v>
       </c>
       <c r="F83">
-        <v>-4.683433709604186</v>
+        <v>-4.558208580955582</v>
       </c>
       <c r="G83">
-        <v>-2.636830809424599</v>
+        <v>-1.152292804885838</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.971113472759893</v>
       </c>
       <c r="E84">
-        <v>-12.75467101453754</v>
+        <v>-13.31717994187432</v>
       </c>
       <c r="F84">
-        <v>-4.803060731344671</v>
+        <v>-4.623594105160755</v>
       </c>
       <c r="G84">
-        <v>-2.542076374999579</v>
+        <v>-1.334650895371052</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.741723257975494</v>
       </c>
       <c r="E85">
-        <v>-14.65139518180622</v>
+        <v>-14.44592020218219</v>
       </c>
       <c r="F85">
-        <v>-4.872795184414542</v>
+        <v>-5.100883663673177</v>
       </c>
       <c r="G85">
-        <v>-2.448781891157378</v>
+        <v>-1.433828218636539</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.545274980129822</v>
       </c>
       <c r="E86">
-        <v>-15.94571909420456</v>
+        <v>-15.26247199287527</v>
       </c>
       <c r="F86">
-        <v>-5.142290436669514</v>
+        <v>-5.188824803889179</v>
       </c>
       <c r="G86">
-        <v>-2.883787575017612</v>
+        <v>-0.6239098735449211</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.389792330526601</v>
       </c>
       <c r="E87">
-        <v>-16.95613938564001</v>
+        <v>-16.91951308786598</v>
       </c>
       <c r="F87">
-        <v>-5.528185391263663</v>
+        <v>-5.418000101180287</v>
       </c>
       <c r="G87">
-        <v>-2.125811689437159</v>
+        <v>-1.151101008491701</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.28471592398347</v>
       </c>
       <c r="E88">
-        <v>-17.95887032821044</v>
+        <v>-17.56061368160588</v>
       </c>
       <c r="F88">
-        <v>-5.641236004193323</v>
+        <v>-5.647269832355315</v>
       </c>
       <c r="G88">
-        <v>-2.401662896496931</v>
+        <v>-1.064814949556136</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.242007455766186</v>
       </c>
       <c r="E89">
-        <v>-18.39532012459571</v>
+        <v>-19.22893067687568</v>
       </c>
       <c r="F89">
-        <v>-5.742136124058719</v>
+        <v>-5.742597524702079</v>
       </c>
       <c r="G89">
-        <v>-2.286227484088084</v>
+        <v>-1.124808655818809</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.269785414256139</v>
       </c>
       <c r="E90">
-        <v>-21.79379042771006</v>
+        <v>-20.61024204648735</v>
       </c>
       <c r="F90">
-        <v>-5.732464106263633</v>
+        <v>-5.815642133913537</v>
       </c>
       <c r="G90">
-        <v>-3.069992519419459</v>
+        <v>-1.068509518377963</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.376924014014858</v>
       </c>
       <c r="E91">
-        <v>-23.30103865947504</v>
+        <v>-22.75415296746472</v>
       </c>
       <c r="F91">
-        <v>-5.890760146734201</v>
+        <v>-6.15414121918911</v>
       </c>
       <c r="G91">
-        <v>-2.389744932555554</v>
+        <v>-1.335180582657336</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.569059139916083</v>
       </c>
       <c r="E92">
-        <v>-24.94897299323632</v>
+        <v>-25.56795199144875</v>
       </c>
       <c r="F92">
-        <v>-6.100492832714203</v>
+        <v>-6.33370393599175</v>
       </c>
       <c r="G92">
-        <v>-2.82387994293896</v>
+        <v>-0.8871578337366873</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.849400449489517</v>
       </c>
       <c r="E93">
-        <v>-27.31418138202053</v>
+        <v>-26.15347009521851</v>
       </c>
       <c r="F93">
-        <v>-6.248942898235097</v>
+        <v>-6.58326701180056</v>
       </c>
       <c r="G93">
-        <v>-3.622135236095725</v>
+        <v>-1.621274617615612</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.214208944580881</v>
       </c>
       <c r="E94">
-        <v>-29.48715604917913</v>
+        <v>-29.3252585749309</v>
       </c>
       <c r="F94">
-        <v>-6.224164772482557</v>
+        <v>-6.939520495620335</v>
       </c>
       <c r="G94">
-        <v>-3.867380449644934</v>
+        <v>-2.020917054025352</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.657632735548169</v>
       </c>
       <c r="E95">
-        <v>-30.75300718125423</v>
+        <v>-31.88268257144469</v>
       </c>
       <c r="F95">
-        <v>-6.310321195129227</v>
+        <v>-7.043829347348251</v>
       </c>
       <c r="G95">
-        <v>-4.194041909641441</v>
+        <v>-2.340712442573409</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.170639175851312</v>
       </c>
       <c r="E96">
-        <v>-33.2815530990211</v>
+        <v>-33.51495291361343</v>
       </c>
       <c r="F96">
-        <v>-6.530552195388608</v>
+        <v>-7.025505446214625</v>
       </c>
       <c r="G96">
-        <v>-3.477656407670852</v>
+        <v>-3.456359668216721</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.728337675459135</v>
       </c>
       <c r="E97">
-        <v>-36.28305284214906</v>
+        <v>-36.49482013640675</v>
       </c>
       <c r="F97">
-        <v>-6.803005547638977</v>
+        <v>-7.297615440176533</v>
       </c>
       <c r="G97">
-        <v>-5.390853780271064</v>
+        <v>-3.286707451511229</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-6.316292728057159</v>
       </c>
       <c r="E98">
-        <v>-39.28923502740095</v>
+        <v>-39.02279320221164</v>
       </c>
       <c r="F98">
-        <v>-6.685662749011711</v>
+        <v>-7.609950541034684</v>
       </c>
       <c r="G98">
-        <v>-5.387669035462284</v>
+        <v>-3.769616729324717</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.89405150042589</v>
       </c>
       <c r="E99">
-        <v>-41.37973486169485</v>
+        <v>-41.98863800524021</v>
       </c>
       <c r="F99">
-        <v>-7.509835713467141</v>
+        <v>-7.648579798129433</v>
       </c>
       <c r="G99">
-        <v>-5.639551892817733</v>
+        <v>-4.737911573015068</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-7.461724740774358</v>
       </c>
       <c r="E100">
-        <v>-43.86065255408604</v>
+        <v>-44.54792546880815</v>
       </c>
       <c r="F100">
-        <v>-7.167237452098814</v>
+        <v>-7.554824761296884</v>
       </c>
       <c r="G100">
-        <v>-6.146707606160843</v>
+        <v>-4.129277707256678</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.956716013331704</v>
       </c>
       <c r="E101">
-        <v>-46.00668959361001</v>
+        <v>-46.92663550284622</v>
       </c>
       <c r="F101">
-        <v>-7.292796412810747</v>
+        <v>-7.680087166478614</v>
       </c>
       <c r="G101">
-        <v>-6.917617793163228</v>
+        <v>-5.159781012175474</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.430728120316779</v>
       </c>
       <c r="E102">
-        <v>-49.63835706210486</v>
+        <v>-48.8721222782295</v>
       </c>
       <c r="F102">
-        <v>-7.176330855263046</v>
+        <v>-7.73744870983657</v>
       </c>
       <c r="G102">
-        <v>-7.221148471476846</v>
+        <v>-6.224220719417339</v>
       </c>
     </row>
   </sheetData>
